--- a/human_resources_surveys/007_employee_benefits_preference_survey--human_resources_surveys.xlsx
+++ b/human_resources_surveys/007_employee_benefits_preference_survey--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,7 +888,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>remote_work_options</t>
+          <t>remote work options</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>flexible_work_schedule</t>
+          <t>flexible work schedule</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>family_days_off</t>
+          <t>family days off</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>health_insurance</t>
+          <t>health insurance</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>financial_support</t>
+          <t>financial support</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>family_leave</t>
+          <t>family leave</t>
         </is>
       </c>
     </row>
